--- a/bases de datos planes y programas/planes_educación_física_y_salud.xlsx
+++ b/bases de datos planes y programas/planes_educación_física_y_salud.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Planes Curriculares" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planes Curriculares'!$A$1:$G$124</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -469,12 +471,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -522,7 +524,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -569,7 +571,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -608,7 +610,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -647,7 +649,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -687,7 +689,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -728,7 +730,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -774,7 +776,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -816,7 +818,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -862,7 +864,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -914,7 +916,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -957,7 +959,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1003,7 +1005,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1058,7 +1060,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1138,7 +1140,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1182,7 +1184,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1224,7 +1226,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1273,7 +1275,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1361,7 +1363,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1411,7 +1413,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1453,7 +1455,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1496,7 +1498,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1549,7 +1551,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1590,7 +1592,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1633,7 +1635,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1676,7 +1678,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1717,7 +1719,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1775,7 +1777,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1817,7 +1819,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1868,7 +1870,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1921,7 +1923,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1962,7 +1964,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2020,7 +2022,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2071,7 +2073,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2113,7 +2115,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2154,7 +2156,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2195,7 +2197,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2236,7 +2238,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2283,7 +2285,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2323,7 +2325,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2368,7 +2370,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2420,7 +2422,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2462,7 +2464,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2515,7 +2517,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2557,7 +2559,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2601,7 +2603,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2644,7 +2646,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -2684,7 +2686,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2723,7 +2725,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -2770,7 +2772,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2815,7 +2817,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -2862,7 +2864,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2911,7 +2913,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2951,7 +2953,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2994,7 +2996,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3036,7 +3038,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3076,7 +3078,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3122,7 +3124,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3162,7 +3164,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3202,7 +3204,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3253,7 +3255,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3298,7 +3300,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3340,7 +3342,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -3393,7 +3395,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3436,7 +3438,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3487,7 +3489,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3548,7 +3550,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -3606,7 +3608,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3675,7 +3677,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3730,7 +3732,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3782,7 +3784,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3822,7 +3824,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3861,7 +3863,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3901,7 +3903,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3939,7 +3941,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -3978,7 +3980,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -4017,7 +4019,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4055,7 +4057,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4107,7 +4109,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -4169,7 +4171,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -4232,7 +4234,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -4294,7 +4296,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -4353,7 +4355,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -4393,7 +4395,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -4432,7 +4434,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -4472,7 +4474,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -4510,7 +4512,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -4549,7 +4551,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4588,7 +4590,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -4626,7 +4628,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -4691,7 +4693,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -4750,7 +4752,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -4812,7 +4814,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -4863,7 +4865,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -4911,7 +4913,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -4963,7 +4965,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5016,7 +5018,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -5072,7 +5074,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5122,7 +5124,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -5181,7 +5183,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5221,7 +5223,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -5261,7 +5263,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -5301,7 +5303,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -5341,7 +5343,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -5380,7 +5382,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
@@ -5420,7 +5422,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -5453,10 +5455,14 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr"/>
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -5492,10 +5498,14 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -5528,10 +5538,14 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr"/>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -5561,33 +5575,255 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
+          <t>HABILIDADES MOTRICES ESPECIALIZADAS, SUS ESTRATEGIAS Y TÁCTICAS</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Evaluar el impacto de las estrategias y tácticas individuales y colectivas utilizadas para la resolución de problemas en el juego, el deporte y la recreación, asumiendo distintos roles y tareas.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>• Registran las estrategias y tácticas utilizadas y su efectividad durante el juego.
+• Registran la influencia las interacciones comunicativas verbales y/o no verbales en las situaciones de juego.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>PLANES DE ENTRENAMIENTO PARA LA CONDICIÓN FÍSICA</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Diseñar y aplicar un plan de entrenamiento para mejorar su rendimiento físico considerando sus características personales y funcionales.</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>• Mejoran su condición física mediante un plan de entrenamiento, considerando sus resultados iniciales.
+• Elaboran un plan de entrenamiento que incluya el principio de sobrecarga.
+• Ejecutan ejercicios que mejoren la fuerza –utilizando su peso corporal– y que respondan a su plan de entrenamiento.
+• Describen las funciones orgánicas que ocurren durante el entrenamiento físico (frecuencia cardíaca, presión arterial, etc.).
+• Mantienen los registros y reportes diarios y/o semanales de las mediciones aplicadas para ajustar su plan de entrenamiento.
+• Colaboran con otros para crear un programa de entrenamiento que requiera usar las habilidades motrices especializadas en diferentes entornos.
+• Aceptan la colaboración de otros para planificar su entrenamiento orientado a mejorar la condición física.
+• Practican para mejorar sus desempeños de diferentes habilidades y destrezas en diversos juegos modificados, deportes y acciones motrices variadas.
+• Practica diariamente actividad física en su tiempo libre, en distintos entornos.
+• Mantiene el registro diario de la actividad física que realiza diariamente, en una plataforma en línea.
+• Manifiesta –en un registro escrito– qué tipo de actividad ejecuta en su plan, utilizando un lenguaje técnico y específico de la asignatura.
+• Registra diariamente la intensidad del trabajo con la escala de Borg y la frecuencia cardíaca en reposo y después de la actividad.
+• Describe en su registro diario el lugar, los materiales y con quién trabajó en su práctica diaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>PROGRAMAS Y PROYECTOS DEPORTIVOS, RECREATIVOS Y SOCIOCULTURALES</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Promover el bienestar, el autocuidado, la vida activa y la alimentación saludable en su comunidad, valorando la diversidad de las personas a través de la aplicación de programas y proyectos deportivos, recreativos y socioculturales.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>• Participan en actividades grupales en su comunidad que promuevan un estilo de vida activa saludable.
+• Participan en diversas estrategias que promueven acciones de prevención y autocuidado, al interior de su establecimiento educacional.
+• Promueven la práctica regular de actividad física al menos 150 minutos semanales, de intensidad moderada a vigorosa.
+• Respetan y aceptan normas básicas del trabajo autónomo en equipo para planificar el proyecto de bienestar para su comunidad.
+• Gestionan y participan en las actividades grupales en su comunidad orientadas a la promoción de un estilo de vida activa y saludable.
+• Proponen una gran variedad de estrategias lúdicas y atractivas en complejidad, que promueven la prevención y autocuidado, al interior del establecimiento educacional.
+• Implementan en su comunidad escolar la práctica regular de actividad física durante al menos 150 minutos semanales, de intensidad moderada a vigorosa, por medio de registros de cada curso y Unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>COMUNIDADES ACTIVAS</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Promover el bienestar, el autocuidado, la vida activa y la alimentación saludable en su comunidad, valorando la diversidad de las personas a través de la aplicación de programas y proyectos deportivos, recreativos y socioculturales.</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>• Organizan campeonatos, jornadas recreativas, encuentros deportivos u otros en su escuela y su comunidad.
+• Establecen alianzas estratégicas para promover una vida activa en su comunidad y/o entorno.
+• Participan de manera autónoma en diferentes actividades físicas y demuestra sus talentos y capacidades.
+• Reconocen cuáles son sus potencialidades y limitaciones y ponen las primeras al servicio de una actividad.
+• Lideran, dirigen y participan en las acciones de trabajo planificadas y no temen a ser ejemplo para sus compañeros.
+• Participan activamente en diversas actividades físicas propuestas por sus pares y están conscientes del trabajo que se requiere para lograr resultados concretos.
+• Identifican las barreras y temores que les dificultan la práctica regular para mejorar su condición física.
+• Proponen estrategias digitales para promover y adquirir un estilo de vida activo saludable, por ejemplo: el uso de monitores cardiacos cuentapasos, relojes inteligentes, entre otros.
+• Participan activamente en la gestión de una actividad recreativa o campeonato deportivo para promover una comunidad activa.
+• Elaboran un registro con antecedentes orientados a gestionar la actividad recreativa o campeonato.
+• Trabajan en equipo, asumiendo construir una comunidad activa.
+• Demuestran iniciativa en la promoción de una vida activa con sus compañeros y en su comunidad escolar.
+• Establecen relaciones positivas bajo un enfoque de derechos y valoran la heterogeneidad sociocultural para construir una comunidad activa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 1  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>COMUNIDADES ACTIVAS</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Analizar por medio de la práctica regular de actividad física cómo los factores sociales, culturales, económicos y tecnológicos favorecen el desarrollo de oportunidades para la adquisición de un estilo de vida activo saludable a nivel local, regional y global.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>• Evalúan los distintos factores sociales que imposibilitan que su comunidad adquiera un estilo de vida activo saludable (falta de espacios públicos, materiales livianos, vestuario).
+• Proponen a su comunidad estrategias digitales de fácil alcance (mediante celulares) para promover que adquiera un estilo de vida activo saludable.
+• Evalúan qué factores sociales son una barrera para adquirir un estilo de vida activo saludable; por ejemplo: escasos espacios públicos para practicar actividad física.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
           <t>HABILIDADES MOTRICES, ESTRATEGIAS Y TÁCTICAS</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>OA 1</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E117" s="5" t="inlineStr">
         <is>
           <t>Evaluar individual y colectivamente las habilidades motrices especializadas utilizadas en una variedad de actividades físicas que sean de su interés y en diferentes entornos.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>• Ejecutan habilidades motrices especializadas en variados juegos modificados y destrezas perceptivo-motrices de su interés.
 • Analizan la habilidad motriz especializada que alcanzaron durante situaciones del juego modificados.
@@ -5604,34 +5840,38 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr"/>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>PLANES DE ENTRENAMIENTO</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>OA 1</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>Evaluar individual y colectivamente las habilidades motrices especializadas utilizadas en una variedad de actividades físicas que sean de su interés y en diferentes entornos.</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>• Utilizan una variedad de habilidades motrices especializadas para desarrollar su rendimiento físico y socioemocional.
 • Colaboran con otros en evaluar y comparar los datos de su curso con relación a las habilidades motrices especializadas.
@@ -5643,67 +5883,75 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr"/>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>PROGRAMAS Y PROYECTOS RECREATIVOS, DEPORTIVOS Y SOCIOCULTURALES</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>OA 1</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>Evaluar individual y colectivamente las habilidades motrices especializadas utilizadas en una variedad de actividades físicas que sean de su interés y en diferentes entornos.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>• Colaboran con otros para evaluar y comparar los datos de su curso en relación con las habilidades motrices especializadas.</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr"/>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>COMUNIDADES ACTIVAS</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>OA 1</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>Evaluar individual y colectivamente las habilidades motrices especializadas utilizadas en una variedad de actividades físicas que sean de su interés y en diferentes entornos.</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>• Despliegan prácticas repetitivas de la habilidad motriz especializada aprendida, para poder transferirla a la situación del juego, reglado o sin reglas.
 • Reconocen la experiencia de otros y la ponen al servicio de todos para mejorar el logro de estilos de vida activos en la comunidad.
@@ -5731,68 +5979,38 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr"/>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>HABILIDADES MOTRICES ESPECIALIZADAS, SUS ESTRATEGIAS Y TÁCTICAS</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>HABILIDADES MOTRICES, ESTRATEGIAS Y TÁCTICAS</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>Evaluar el impacto de las estrategias y tácticas individuales y colectivas utilizadas para la resolución de problemas en el juego, el deporte y la recreación, asumiendo distintos roles y tareas.</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>• Registran las estrategias y tácticas utilizadas y su efectividad durante el juego.
-• Registran la influencia las interacciones comunicativas verbales y/o no verbales en las situaciones de juego.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr"/>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>HABILIDADES MOTRICES, ESTRATEGIAS Y TÁCTICAS</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E121" s="5" t="inlineStr">
         <is>
           <t>Organizar y aplicar individual y colectivamente estrategias y tácticas para desarrollar un juego inteligente, asumiendo distintos roles y tareas.</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>• Analizan la habilidad motriz especializada que alcanzaron durante situaciones del juego modificados.
 • Comunican, de manera individual y colectiva, logros de estrategias y tácticas exploradas en un juego modificado o deporte de su interés.
@@ -5814,79 +6032,38 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr"/>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>PLANES DE ENTRENAMIENTO PARA LA CONDICIÓN FÍSICA</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>PLANES DE ENTRENAMIENTO</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>Diseñar y aplicar un plan de entrenamiento para mejorar su rendimiento físico considerando sus características personales y funcionales.</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>• Mejoran su condición física mediante un plan de entrenamiento, considerando sus resultados iniciales.
-• Elaboran un plan de entrenamiento que incluya el principio de sobrecarga.
-• Ejecutan ejercicios que mejoren la fuerza –utilizando su peso corporal– y que respondan a su plan de entrenamiento.
-• Describen las funciones orgánicas que ocurren durante el entrenamiento físico (frecuencia cardíaca, presión arterial, etc.).
-• Mantienen los registros y reportes diarios y/o semanales de las mediciones aplicadas para ajustar su plan de entrenamiento.
-• Colaboran con otros para crear un programa de entrenamiento que requiera usar las habilidades motrices especializadas en diferentes entornos.
-• Aceptan la colaboración de otros para planificar su entrenamiento orientado a mejorar la condición física.
-• Practican para mejorar sus desempeños de diferentes habilidades y destrezas en diversos juegos modificados, deportes y acciones motrices variadas.
-• Practica diariamente actividad física en su tiempo libre, en distintos entornos.
-• Mantiene el registro diario de la actividad física que realiza diariamente, en una plataforma en línea.
-• Manifiesta –en un registro escrito– qué tipo de actividad ejecuta en su plan, utilizando un lenguaje técnico y específico de la asignatura.
-• Registra diariamente la intensidad del trabajo con la escala de Borg y la frecuencia cardíaca en reposo y después de la actividad.
-• Describe en su registro diario el lugar, los materiales y con quién trabajó en su práctica diaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr"/>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>PLANES DE ENTRENAMIENTO</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>Aplicar responsablemente un plan de entrenamiento para mejorar su rendimiento físico considerando sus características personales y funcionales.</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>• Disponen de habilidades reflexivas y analíticas para revisar los antecedentes de la evaluación de su entrenamiento personal.
 • Asumen responsabilidades en la motivación y conducción del entrenamiento grupal.
@@ -5908,118 +6085,38 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr"/>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>PROGRAMAS Y PROYECTOS DEPORTIVOS, RECREATIVOS Y SOCIOCULTURALES</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Educación Física y Salud</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>PROGRAMAS Y PROYECTOS RECREATIVOS, DEPORTIVOS Y SOCIOCULTURALES</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>Promover el bienestar, el autocuidado, la vida activa y la alimentación saludable en su comunidad, valorando la diversidad de las personas a través de la aplicación de programas y proyectos deportivos, recreativos y socioculturales.</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>• Participan en actividades grupales en su comunidad que promuevan un estilo de vida activa saludable.
-• Participan en diversas estrategias que promueven acciones de prevención y autocuidado, al interior de su establecimiento educacional.
-• Promueven la práctica regular de actividad física al menos 150 minutos semanales, de intensidad moderada a vigorosa.
-• Respetan y aceptan normas básicas del trabajo autónomo en equipo para planificar el proyecto de bienestar para su comunidad.
-• Gestionan y participan en las actividades grupales en su comunidad orientadas a la promoción de un estilo de vida activa y saludable.
-• Proponen una gran variedad de estrategias lúdicas y atractivas en complejidad, que promueven la prevención y autocuidado, al interior del establecimiento educacional.
-• Implementan en su comunidad escolar la práctica regular de actividad física durante al menos 150 minutos semanales, de intensidad moderada a vigorosa, por medio de registros de cada curso y Unidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr"/>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>COMUNIDADES ACTIVAS</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>Promover el bienestar, el autocuidado, la vida activa y la alimentación saludable en su comunidad, valorando la diversidad de las personas a través de la aplicación de programas y proyectos deportivos, recreativos y socioculturales.</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>• Organizan campeonatos, jornadas recreativas, encuentros deportivos u otros en su escuela y su comunidad.
-• Establecen alianzas estratégicas para promover una vida activa en su comunidad y/o entorno.
-• Participan de manera autónoma en diferentes actividades físicas y demuestra sus talentos y capacidades.
-• Reconocen cuáles son sus potencialidades y limitaciones y ponen las primeras al servicio de una actividad.
-• Lideran, dirigen y participan en las acciones de trabajo planificadas y no temen a ser ejemplo para sus compañeros.
-• Participan activamente en diversas actividades físicas propuestas por sus pares y están conscientes del trabajo que se requiere para lograr resultados concretos.
-• Identifican las barreras y temores que les dificultan la práctica regular para mejorar su condición física.
-• Proponen estrategias digitales para promover y adquirir un estilo de vida activo saludable, por ejemplo: el uso de monitores cardiacos cuentapasos, relojes inteligentes, entre otros.
-• Participan activamente en la gestión de una actividad recreativa o campeonato deportivo para promover una comunidad activa.
-• Elaboran un registro con antecedentes orientados a gestionar la actividad recreativa o campeonato.
-• Trabajan en equipo, asumiendo construir una comunidad activa.
-• Demuestran iniciativa en la promoción de una vida activa con sus compañeros y en su comunidad escolar.
-• Establecen relaciones positivas bajo un enfoque de derechos y valoran la heterogeneidad sociocultural para construir una comunidad activa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr"/>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>PROGRAMAS Y PROYECTOS RECREATIVOS, DEPORTIVOS Y SOCIOCULTURALES</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>Evaluar el impacto de variados programas y proyectos deportivos, recreativos y socioculturales que promuevan de manera colectiva el bienestar, el autocuidado, la vida activa y la alimentación saludable en su comunidad, considerando la diversidad de las personas.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G123" s="5" t="inlineStr">
         <is>
           <t>• Colaboran con otros para evaluar y comparar los datos de su curso en relación con las habilidades motrices especializadas.
 • Desarrollan habilidades para observar la realidad en que se implementa la actividad física que se practica.
@@ -6036,46 +6133,15 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr"/>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Educación física y salud</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>COMUNIDADES ACTIVAS</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>Analizar por medio de la práctica regular de actividad física cómo los factores sociales, culturales, económicos y tecnológicos favorecen el desarrollo de oportunidades para la adquisición de un estilo de vida activo saludable a nivel local, regional y global.</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>• Evalúan los distintos factores sociales que imposibilitan que su comunidad adquiera un estilo de vida activo saludable (falta de espacios públicos, materiales livianos, vestuario).
-• Proponen a su comunidad estrategias digitales de fácil alcance (mediante celulares) para promover que adquiera un estilo de vida activo saludable.
-• Evalúan qué factores sociales son una barrera para adquirir un estilo de vida activo saludable; por ejemplo: escasos espacios públicos para practicar actividad física.</t>
-        </is>
-      </c>
-    </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Programa FG electivo  Educación física y salud 2  3° y 4° medio</t>
+        </is>
+      </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Educación física y salud</t>
+          <t>Educación Física y Salud</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -6126,6 +6192,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>